--- a/movimentacoes.xlsx
+++ b/movimentacoes.xlsx
@@ -16,9 +16,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,7 +50,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -447,147 +446,6 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>RODO CABO DE ALUMINIO</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Entrada</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>15</v>
-      </c>
-      <c r="D2" s="1" t="n">
-        <v>46140.35643451389</v>
-      </c>
-      <c r="E2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>PERNEIRA</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Entrada</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D3" s="1" t="n">
-        <v>46140.35643489583</v>
-      </c>
-      <c r="E3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>LUVA NITRILICA</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Entrada</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" s="1" t="n">
-        <v>46140.35643496528</v>
-      </c>
-      <c r="E4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>COADOR DE PANO</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Entrada</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>5</v>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>46140.42104399305</v>
-      </c>
-      <c r="E5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>PERNEIRA</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Entrada</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>2</v>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>46140.42104481482</v>
-      </c>
-      <c r="E6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>PERNEIRA</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Saída</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>2</v>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>46140.42219203704</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>TMG - TROPICAL MELHORAMENTO GENETICO</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>LUVA NITRILICA</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Saída</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>5</v>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>46140.42688856399</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>CONDOMINIO COSTA BRAVA</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/movimentacoes.xlsx
+++ b/movimentacoes.xlsx
@@ -16,16 +16,17 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
-  </numFmts>
-  <fonts count="1">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -36,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -44,13 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -416,33 +425,38 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>produto</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>tipo</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>quantidade</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>data</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>cliente</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>observacao</t>
         </is>
       </c>
     </row>
